--- a/data/zhk_registry.xlsx
+++ b/data/zhk_registry.xlsx
@@ -22213,7 +22213,7 @@
         <v>1</v>
       </c>
       <c r="AS99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT99" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>1</v>
       </c>
       <c r="AS107" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT107" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>1</v>
       </c>
       <c r="AS121" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT121" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>запретная зона Uzum, рекомендуемой рядом нет — открыть нельзя; объявлений рядом нет; 828 квартир; сдача 2027 (−)</t>
+          <t>запретная зона Uzum, рекомендуемой рядом нет — открыть нельзя; объявлений рядом нет; 828 квартир; сдача 2027 (−); ПВЗ Uzum в 230 м (уже обслужен)</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -32468,13 +32468,13 @@
         <v>7</v>
       </c>
       <c r="AQ146" t="n">
-        <v>631</v>
+        <v>230</v>
       </c>
       <c r="AR146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT146" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>2</v>
       </c>
       <c r="AS151" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT151" t="inlineStr">
         <is>

--- a/data/zhk_registry.xlsx
+++ b/data/zhk_registry.xlsx
@@ -2471,7 +2471,7 @@
         <v>1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1652</v>
+        <v>1581</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>

--- a/data/zhk_registry.xlsx
+++ b/data/zhk_registry.xlsx
@@ -2294,7 +2294,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>да: 176 м</t>
+          <t>да: 83 м</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
